--- a/excel/universities/abo-akademi-university.xlsx
+++ b/excel/universities/abo-akademi-university.xlsx
@@ -115,7 +115,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.abo.fi/en/study/apply/</t>
+          <t xml:space="preserve">https://www.abo.fi/en/study/apply/international-master-programmes/application-process/</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -125,7 +125,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">International master's degree programmes</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -140,12 +140,12 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">University-wide tuition fee scholarship scheme</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fill program-specific information here</t>
+          <t xml:space="preserve">International master's programmes taught in English use the January national application period.</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -229,7 +229,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">International master's degree programmes</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -239,12 +239,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2026-01-07</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2026-01-21</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -254,12 +254,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.abo.fi/en/study/apply/</t>
+          <t xml:space="preserve">https://www.abo.fi/en/study/apply/international-master-programmes/application-process/</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify annual deadlines</t>
+          <t xml:space="preserve">Attachment deadline 2026-01-28; admission results sent in the beginning of April 2026.</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -275,7 +275,7 @@
 
 <file path=xl\worksheets\sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -333,30 +333,156 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">International master's degree programmes</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Passport</t>
+          <t xml:space="preserve">Degree certificate</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t xml:space="preserve">If graduated</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Upload scans of original documents and translations if needed.</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.abo.fi/en/study/apply/international-master-programmes/application-process/</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Abo Akademi University</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Master</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">International master's degree programmes</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Transcript of records</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t xml:space="preserve">Yes</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.abo.fi/en/study/apply/</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
+      <c r="F3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">If still graduating state expected graduation date and upload studies completed so far.</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.abo.fi/en/study/apply/international-master-programmes/application-process/</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Abo Akademi University</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Master</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">International master's degree programmes</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proof of language proficiency</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Applicants must meet university and programme-specific language requirements.</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.abo.fi/en/study/apply/international-master-programmes/</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Abo Akademi University</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Master</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">International master's degree programmes</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Scholarship application</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Optional</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tuition-fee-paying applicants apply for scholarships through the application form where available.</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.abo.fi/en/study/apply/international-master-programmes/application-process/</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-03-14</t>
         </is>
@@ -369,7 +495,7 @@
 
 <file path=xl\worksheets\sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -420,15 +546,30 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
+          <t xml:space="preserve">citation_source</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">citation_last_checked</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
           <t xml:space="preserve">official_profile_url</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t xml:space="preserve">email</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="N1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">notes</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
         <is>
           <t xml:space="preserve">last_verified</t>
         </is>
@@ -437,7 +578,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Abo Akademi University</t>
+          <t xml:space="preserve">University Name</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -457,7 +598,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Research Area 1; Research Area 2</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -482,7 +623,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.abo.fi/en/</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -492,7 +633,22 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-03-14</t>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
         </is>
       </c>
     </row>

--- a/excel/universities/abo-akademi-university.xlsx
+++ b/excel/universities/abo-akademi-university.xlsx
@@ -495,7 +495,7 @@
 
 <file path=xl\worksheets\sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:O3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,17 +578,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">University Name</t>
+          <t xml:space="preserve">Abo Akademi University</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Department Name</t>
+          <t xml:space="preserve">Computer Science</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Professor Name</t>
+          <t xml:space="preserve">Ivan Porres</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -598,7 +598,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Software engineering; Distributed systems; Formal methods; Process modeling</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -623,17 +623,17 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Abo Akademi official profile</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2026-03-14</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">https://www.abo.fi/en/people/ivan-porres/</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -648,7 +648,84 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Abo Akademi official profile used for title and research focus.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Abo Akademi University</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Computer Science</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Johan Lilius</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Professor</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Embedded systems; Dependable systems; Software engineering; Computer architecture</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Abo Akademi official profile</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.abo.fi/en/people/johan-lilius/</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Abo Akademi official profile used for title and research focus.</t>
         </is>
       </c>
     </row>

--- a/excel/universities/abo-akademi-university.xlsx
+++ b/excel/universities/abo-akademi-university.xlsx
@@ -20,7 +20,8 @@
     <sheet name="UniversityInfo" sheetId="1" r:id="rId1"/>
     <sheet name="Deadlines" sheetId="2" r:id="rId2"/>
     <sheet name="Documents" sheetId="3" r:id="rId3"/>
-    <sheet name="Professors" sheetId="4" r:id="rId4"/>
+    <sheet name="Departments" sheetId="4" r:id="rId4"/>
+    <sheet name="Professors" sheetId="5" r:id="rId5"/>
   </sheets>
 </workbook>
 </file>
@@ -495,6 +496,392 @@
 
 <file path=xl\worksheets\sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:I8"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">university_name</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unit_type</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unit_name</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">parent_unit</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">campus_or_city</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">focus_areas</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">official_url</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">notes</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">last_verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Abo Akademi University</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty of Arts, Psychology and Theology</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Turku</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Arts; Psychology; Theology</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.abo.fi/en/news/faculties-at-abo-akademi-university-from-january-1-2025/</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official university announcement of faculty structure.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Abo Akademi University</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty of Social Sciences, Business and Economics, and Law</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Turku</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Social sciences; Business; Economics; Law</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.abo.fi/en/news/faculties-at-abo-akademi-university-from-january-1-2025/</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official university announcement of faculty structure.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Abo Akademi University</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty of Science and Engineering</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Turku</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Science; Engineering; IT</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.abo.fi/en/news/faculties-at-abo-akademi-university-from-january-1-2025/</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official university announcement of faculty structure.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Abo Akademi University</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty of Education and Welfare Studies</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vaasa</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Education; Welfare studies</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.abo.fi/en/news/faculties-at-abo-akademi-university-from-january-1-2025/</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official university announcement of faculty structure.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Abo Akademi University</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Department</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Department of Business and Economics</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty of Social Sciences, Business and Economics, and Law</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Turku</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Business; Economics</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.abo.fi/en/about-abo-akademi-university/organisation/faculty-of-social-sciences-business-and-economics-and-law/department-of-business-and-economics/</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official department page.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Abo Akademi University</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Department</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Department of Law</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty of Social Sciences, Business and Economics, and Law</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Turku</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Law</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.abo.fi/en/news/faculties-at-abo-akademi-university-from-january-1-2025/</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Department listed in official faculty announcement.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Abo Akademi University</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Department</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Department of Computer Science</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty of Science and Engineering</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Turku</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Computer science</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.abo.fi/en/subject/computer-science/</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Department or subject page used as official academic unit reference.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl\worksheets\sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:O3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
